--- a/artfynd/A 9091-2020 artfynd.xlsx
+++ b/artfynd/A 9091-2020 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455599</v>
+        <v>117455554</v>
       </c>
       <c r="B3" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>483951</v>
+        <v>484109</v>
       </c>
       <c r="R3" t="n">
-        <v>7084261</v>
+        <v>7084326</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455554</v>
+        <v>117455599</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484109</v>
+        <v>483951</v>
       </c>
       <c r="R4" t="n">
-        <v>7084326</v>
+        <v>7084261</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 9091-2020 artfynd.xlsx
+++ b/artfynd/A 9091-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117455553</v>
+        <v>117455599</v>
       </c>
       <c r="B2" t="n">
-        <v>90499</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>483812</v>
+        <v>483951</v>
       </c>
       <c r="R2" t="n">
-        <v>7084247</v>
+        <v>7084261</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-05-30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117455554</v>
+        <v>117455553</v>
       </c>
       <c r="B3" t="n">
-        <v>90499</v>
+        <v>90501</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484109</v>
+        <v>483812</v>
       </c>
       <c r="R3" t="n">
-        <v>7084326</v>
+        <v>7084247</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117455599</v>
+        <v>117455554</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>483951</v>
+        <v>484109</v>
       </c>
       <c r="R4" t="n">
-        <v>7084261</v>
+        <v>7084326</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-05-30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,7 +989,7 @@
         <v>117455593</v>
       </c>
       <c r="B5" t="n">
-        <v>57287</v>
+        <v>57288</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
